--- a/February 2026.xlsx
+++ b/February 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abutalib/Projects/personal-accounting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3BB5443-34EF-4B46-A0B9-8478553BB90F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35CAA92E-D3D3-0046-A520-6463395E2F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19800" xr2:uid="{7E62CB60-3E82-0E48-87C0-051D0E492E72}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19800" activeTab="1" xr2:uid="{7E62CB60-3E82-0E48-87C0-051D0E492E72}"/>
   </bookViews>
   <sheets>
     <sheet name="مصاريف الشهر" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="135">
   <si>
     <t>فاتورة الكهرباء</t>
   </si>
@@ -267,12 +267,6 @@
     <t>سلفة من الادخار</t>
   </si>
   <si>
-    <t>سلف من معاذ</t>
-  </si>
-  <si>
-    <t>دفعة مقدمة لأمي</t>
-  </si>
-  <si>
     <t>إجمالي التحويل لمعاذ</t>
   </si>
   <si>
@@ -439,6 +433,15 @@
   </si>
   <si>
     <t>الراجحي</t>
+  </si>
+  <si>
+    <t>تأخير جيم ناشن</t>
+  </si>
+  <si>
+    <t>تأخير شات جبت</t>
+  </si>
+  <si>
+    <t>إجمالي التحويل المتأخر لتكمو</t>
   </si>
 </sst>
 </file>
@@ -488,7 +491,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -510,6 +513,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -551,7 +560,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -579,6 +588,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -935,7 +945,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C2F52D6-F91F-A540-B517-60C5A16A2B32}">
-  <dimension ref="A1:AF40"/>
+  <dimension ref="A1:AF45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="22" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -1002,11 +1012,11 @@
       </c>
       <c r="X1" s="4"/>
       <c r="Y1" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AB1" s="4"/>
       <c r="AC1" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -1048,7 +1058,7 @@
       </c>
       <c r="W2" s="3">
         <f>SUM(W7:W16)</f>
-        <v>11068</v>
+        <v>17607</v>
       </c>
       <c r="X2" s="4"/>
       <c r="Y2" s="3" t="s">
@@ -1056,7 +1066,7 @@
       </c>
       <c r="AA2" s="3">
         <f>SUM(AA7:AB41)</f>
-        <v>26763</v>
+        <v>32533</v>
       </c>
       <c r="AB2" s="4"/>
       <c r="AC2" s="3" t="s">
@@ -1102,8 +1112,8 @@
         <v>20</v>
       </c>
       <c r="AD3" s="3">
-        <f>AA20-AD2</f>
-        <v>0</v>
+        <f>AA21-AD2</f>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.3">
@@ -1166,13 +1176,13 @@
       <c r="C6" s="9"/>
       <c r="I6" s="9"/>
       <c r="K6" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="N6" s="8" t="s">
         <v>61</v>
@@ -1198,7 +1208,7 @@
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E7" s="3">
         <v>200</v>
@@ -1223,7 +1233,7 @@
       </c>
       <c r="R7" s="4"/>
       <c r="S7" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="T7" s="3">
         <v>50</v>
@@ -1245,17 +1255,15 @@
       </c>
       <c r="AB7" s="4"/>
       <c r="AC7" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AD7" s="11">
         <v>1580</v>
       </c>
       <c r="AE7" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="AF7" s="12">
-        <v>-80</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="AF7" s="12"/>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -1266,7 +1274,7 @@
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E8" s="3">
         <v>60</v>
@@ -1291,7 +1299,7 @@
       </c>
       <c r="R8" s="4"/>
       <c r="S8" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="T8" s="3">
         <v>36</v>
@@ -1308,18 +1316,15 @@
       <c r="Y8" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="Z8" s="3">
-        <v>1500</v>
-      </c>
       <c r="AB8" s="4"/>
       <c r="AC8" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AD8" s="11">
         <v>450</v>
       </c>
       <c r="AE8" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.3">
@@ -1331,7 +1336,7 @@
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E9" s="3">
         <v>300</v>
@@ -1352,7 +1357,7 @@
       </c>
       <c r="R9" s="4"/>
       <c r="S9" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="T9" s="3">
         <v>512</v>
@@ -1369,8 +1374,9 @@
       <c r="Y9" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="Z9" s="3">
-        <v>286</v>
+      <c r="AA9" s="11">
+        <f>SUM(Z7:Z8)</f>
+        <v>800</v>
       </c>
       <c r="AB9" s="4"/>
       <c r="AC9" s="3" t="s">
@@ -1380,7 +1386,7 @@
         <v>80</v>
       </c>
       <c r="AE9" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.3">
@@ -1392,7 +1398,7 @@
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F10" s="3">
         <v>1000</v>
@@ -1409,7 +1415,7 @@
       </c>
       <c r="R10" s="4"/>
       <c r="S10" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="T10" s="3">
         <v>108</v>
@@ -1419,15 +1425,9 @@
         <v>56</v>
       </c>
       <c r="W10" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="X10" s="4"/>
-      <c r="Y10" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="Z10" s="3">
-        <v>-500</v>
-      </c>
       <c r="AB10" s="4"/>
       <c r="AC10" s="3" t="s">
         <v>5</v>
@@ -1436,7 +1436,7 @@
         <v>80</v>
       </c>
       <c r="AE10" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.3">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E11" s="3">
         <v>400</v>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="R11" s="4"/>
       <c r="S11" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="T11" s="3">
         <v>562</v>
@@ -1478,22 +1478,21 @@
         <v>313</v>
       </c>
       <c r="X11" s="4"/>
-      <c r="Y11" s="3" t="s">
-        <v>78</v>
+      <c r="Y11" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="AA11" s="11">
-        <f>SUM(Z7:Z10)</f>
-        <v>2086</v>
+        <v>3000</v>
       </c>
       <c r="AB11" s="4"/>
       <c r="AC11" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AD11" s="11">
         <v>120</v>
       </c>
       <c r="AE11" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.3">
@@ -1515,7 +1514,7 @@
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K12" s="3">
         <v>120</v>
@@ -1525,7 +1524,7 @@
       </c>
       <c r="R12" s="4"/>
       <c r="S12" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="T12" s="3">
         <v>64</v>
@@ -1536,7 +1535,7 @@
       </c>
       <c r="W12" s="3">
         <f>J32</f>
-        <v>7529</v>
+        <v>12568</v>
       </c>
       <c r="X12" s="4"/>
       <c r="AB12" s="4"/>
@@ -1547,7 +1546,7 @@
         <v>77</v>
       </c>
       <c r="AE12" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.3">
@@ -1559,7 +1558,7 @@
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F13" s="3">
         <v>836</v>
@@ -1578,10 +1577,10 @@
       <c r="U13" s="4"/>
       <c r="X13" s="4"/>
       <c r="Y13" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="AA13" s="11">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="AB13" s="4"/>
       <c r="AC13" s="3" t="s">
@@ -1591,7 +1590,7 @@
         <v>150</v>
       </c>
       <c r="AE13" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.3">
@@ -1603,7 +1602,7 @@
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F14" s="3">
         <v>963</v>
@@ -1651,18 +1650,19 @@
       <c r="R15" s="4"/>
       <c r="U15" s="4"/>
       <c r="X15" s="4"/>
-      <c r="Y15" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA15" s="11">
-        <v>1000</v>
+      <c r="Y15" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z15" s="3">
+        <f>K26</f>
+        <v>1537</v>
       </c>
       <c r="AB15" s="4"/>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.3">
       <c r="C16" s="4"/>
       <c r="D16" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F16" s="3">
         <v>168</v>
@@ -1680,6 +1680,12 @@
       <c r="R16" s="4"/>
       <c r="U16" s="4"/>
       <c r="X16" s="4"/>
+      <c r="Y16" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z16" s="3">
+        <v>1000</v>
+      </c>
       <c r="AB16" s="4"/>
     </row>
     <row r="17" spans="3:28" x14ac:dyDescent="0.3">
@@ -1705,24 +1711,23 @@
       <c r="U17" s="4"/>
       <c r="X17" s="4"/>
       <c r="Y17" s="3" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="Z17" s="3">
-        <f>K26</f>
-        <v>1537</v>
+        <v>300</v>
       </c>
       <c r="AB17" s="4"/>
     </row>
     <row r="18" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C18" s="4"/>
       <c r="D18" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F18" s="3">
         <v>150</v>
       </c>
       <c r="I18" s="4"/>
-      <c r="J18" s="3" t="s">
+      <c r="J18" s="19" t="s">
         <v>11</v>
       </c>
       <c r="K18" s="3">
@@ -1735,17 +1740,17 @@
       <c r="U18" s="4"/>
       <c r="X18" s="4"/>
       <c r="Y18" s="3" t="s">
-        <v>83</v>
+        <v>132</v>
       </c>
       <c r="Z18" s="3">
-        <v>1000</v>
+        <v>-150</v>
       </c>
       <c r="AB18" s="4"/>
     </row>
     <row r="19" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C19" s="4"/>
       <c r="D19" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E19" s="3">
         <v>200</v>
@@ -1764,17 +1769,17 @@
       <c r="U19" s="4"/>
       <c r="X19" s="4"/>
       <c r="Y19" s="3" t="s">
-        <v>69</v>
+        <v>133</v>
       </c>
       <c r="Z19" s="3">
-        <v>0</v>
+        <v>-77</v>
       </c>
       <c r="AB19" s="4"/>
     </row>
     <row r="20" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C20" s="4"/>
       <c r="D20" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F20" s="3">
         <v>100</v>
@@ -1792,25 +1797,18 @@
       <c r="R20" s="4"/>
       <c r="U20" s="4"/>
       <c r="X20" s="4"/>
-      <c r="Y20" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AA20" s="11">
-        <f>SUM(Z17:Z19)</f>
-        <v>2537</v>
-      </c>
       <c r="AB20" s="4"/>
     </row>
     <row r="21" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C21" s="4"/>
       <c r="D21" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F21" s="3">
         <v>70</v>
       </c>
       <c r="I21" s="4"/>
-      <c r="J21" s="3" t="s">
+      <c r="J21" s="19" t="s">
         <v>14</v>
       </c>
       <c r="K21" s="3">
@@ -1822,12 +1820,19 @@
       <c r="R21" s="4"/>
       <c r="U21" s="4"/>
       <c r="X21" s="4"/>
+      <c r="Y21" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA21" s="11">
+        <f>SUM(Z15:Z20)</f>
+        <v>2610</v>
+      </c>
       <c r="AB21" s="4"/>
     </row>
     <row r="22" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C22" s="4"/>
       <c r="D22" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F22" s="3">
         <v>100</v>
@@ -1845,19 +1850,12 @@
       <c r="R22" s="4"/>
       <c r="U22" s="4"/>
       <c r="X22" s="4"/>
-      <c r="Y22" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA22" s="11">
-        <f>L26</f>
-        <v>820</v>
-      </c>
       <c r="AB22" s="4"/>
     </row>
     <row r="23" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C23" s="4"/>
       <c r="D23" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E23" s="3">
         <v>200</v>
@@ -1875,19 +1873,26 @@
       <c r="R23" s="4"/>
       <c r="U23" s="4"/>
       <c r="X23" s="4"/>
+      <c r="Y23" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA23" s="11">
+        <f>L26</f>
+        <v>820</v>
+      </c>
       <c r="AB23" s="4"/>
     </row>
     <row r="24" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C24" s="4"/>
       <c r="D24" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F24" s="3">
         <v>235</v>
       </c>
       <c r="I24" s="4"/>
       <c r="J24" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K24" s="3">
         <v>450</v>
@@ -1898,18 +1903,12 @@
       <c r="R24" s="4"/>
       <c r="U24" s="4"/>
       <c r="X24" s="4"/>
-      <c r="Y24" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="AA24" s="11">
-        <v>2000</v>
-      </c>
       <c r="AB24" s="4"/>
     </row>
     <row r="25" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C25" s="4"/>
       <c r="D25" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E25" s="3">
         <v>350</v>
@@ -1918,12 +1917,18 @@
       <c r="R25" s="4"/>
       <c r="U25" s="4"/>
       <c r="X25" s="4"/>
+      <c r="Y25" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA25" s="11">
+        <v>2000</v>
+      </c>
       <c r="AB25" s="4"/>
     </row>
     <row r="26" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C26" s="3"/>
       <c r="D26" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F26" s="3">
         <v>597</v>
@@ -1951,13 +1956,6 @@
       <c r="R26" s="3"/>
       <c r="U26" s="3"/>
       <c r="X26" s="3"/>
-      <c r="Y26" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="AA26" s="13">
-        <f>T2</f>
-        <v>1332</v>
-      </c>
       <c r="AB26" s="3"/>
     </row>
     <row r="27" spans="3:28" x14ac:dyDescent="0.3">
@@ -1966,6 +1964,13 @@
       <c r="R27" s="3"/>
       <c r="U27" s="3"/>
       <c r="X27" s="3"/>
+      <c r="Y27" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="AA27" s="13">
+        <f>T2</f>
+        <v>1332</v>
+      </c>
       <c r="AB27" s="3"/>
     </row>
     <row r="28" spans="3:28" x14ac:dyDescent="0.3">
@@ -1974,13 +1979,6 @@
       <c r="R28" s="3"/>
       <c r="U28" s="3"/>
       <c r="X28" s="3"/>
-      <c r="Y28" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="AA28" s="11">
-        <f>M26</f>
-        <v>880</v>
-      </c>
       <c r="AB28" s="3"/>
     </row>
     <row r="29" spans="3:28" x14ac:dyDescent="0.3">
@@ -1989,6 +1987,13 @@
       <c r="R29" s="3"/>
       <c r="U29" s="3"/>
       <c r="X29" s="3"/>
+      <c r="Y29" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AA29" s="11">
+        <f>M26</f>
+        <v>880</v>
+      </c>
       <c r="AB29" s="3"/>
     </row>
     <row r="30" spans="3:28" x14ac:dyDescent="0.3">
@@ -1997,22 +2002,15 @@
       <c r="R30" s="3"/>
       <c r="U30" s="3"/>
       <c r="X30" s="3"/>
-      <c r="Y30" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="AA30" s="10">
-        <f>W2</f>
-        <v>11068</v>
-      </c>
       <c r="AB30" s="3"/>
     </row>
     <row r="31" spans="3:28" ht="46" x14ac:dyDescent="0.3">
       <c r="C31" s="3"/>
       <c r="D31" s="16" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="s">
@@ -2030,6 +2028,13 @@
       <c r="R31" s="3"/>
       <c r="U31" s="3"/>
       <c r="X31" s="3"/>
+      <c r="Y31" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA31" s="10">
+        <f>W2</f>
+        <v>17607</v>
+      </c>
       <c r="AB31" s="3"/>
     </row>
     <row r="32" spans="3:28" x14ac:dyDescent="0.3">
@@ -2044,7 +2049,7 @@
       <c r="I32" s="3"/>
       <c r="J32" s="3">
         <f>الأرصدة!M29-'مصاريف الشهر'!D32</f>
-        <v>7529</v>
+        <v>12568</v>
       </c>
       <c r="O32" s="3">
         <f>E3</f>
@@ -2056,17 +2061,11 @@
       </c>
       <c r="Q32" s="3">
         <f>J32-SUM(O32:P32)</f>
-        <v>0</v>
+        <v>5039</v>
       </c>
       <c r="R32" s="3"/>
       <c r="U32" s="3"/>
       <c r="X32" s="3"/>
-      <c r="Y32" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>2000</v>
-      </c>
       <c r="AB32" s="3"/>
     </row>
     <row r="33" spans="3:28" x14ac:dyDescent="0.3">
@@ -2076,11 +2075,10 @@
       <c r="U33" s="3"/>
       <c r="X33" s="3"/>
       <c r="Y33" s="3" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="Z33" s="3">
-        <f>G5</f>
-        <v>40</v>
+        <v>2000</v>
       </c>
       <c r="AB33" s="3"/>
     </row>
@@ -2091,10 +2089,11 @@
       <c r="U34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3" t="s">
-        <v>104</v>
+        <v>20</v>
       </c>
       <c r="Z34" s="3">
-        <v>-500</v>
+        <f>G5</f>
+        <v>40</v>
       </c>
       <c r="AB34" s="3"/>
     </row>
@@ -2104,6 +2103,12 @@
       <c r="R35" s="3"/>
       <c r="U35" s="3"/>
       <c r="X35" s="3"/>
+      <c r="Y35" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z35" s="3">
+        <v>-56</v>
+      </c>
       <c r="AB35" s="3"/>
     </row>
     <row r="36" spans="3:28" x14ac:dyDescent="0.3">
@@ -2112,32 +2117,59 @@
       <c r="R36" s="3"/>
       <c r="U36" s="3"/>
       <c r="X36" s="3"/>
-      <c r="Y36" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="AA36" s="10">
-        <f>SUM(Z32:Z34)</f>
-        <v>1540</v>
-      </c>
       <c r="AB36" s="3"/>
     </row>
-    <row r="38" spans="3:28" x14ac:dyDescent="0.3">
-      <c r="Y38" s="3" t="s">
-        <v>103</v>
+    <row r="37" spans="3:28" x14ac:dyDescent="0.3">
+      <c r="Y37" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA37" s="10">
+        <f>SUM(Z33:Z35)</f>
+        <v>1984</v>
       </c>
     </row>
     <row r="39" spans="3:28" x14ac:dyDescent="0.3">
       <c r="Y39" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z39" s="3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="40" spans="3:28" x14ac:dyDescent="0.3">
+      <c r="Y40" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z40" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="40" spans="3:28" x14ac:dyDescent="0.3">
-      <c r="AA40" s="11">
-        <f>SUM(Z39:Z39)</f>
+    <row r="41" spans="3:28" x14ac:dyDescent="0.3">
+      <c r="AA41" s="11">
+        <f>SUM(Z40:Z40)</f>
         <v>500</v>
+      </c>
+    </row>
+    <row r="43" spans="3:28" x14ac:dyDescent="0.3">
+      <c r="Y43" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z43" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="44" spans="3:28" x14ac:dyDescent="0.3">
+      <c r="Y44" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z44" s="3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="45" spans="3:28" x14ac:dyDescent="0.3">
+      <c r="Y45" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="AA45" s="11">
+        <f>SUM(Z43:Z44)</f>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -2161,7 +2193,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F05345A-5E98-0C43-BBDD-1D2CC38375ED}">
-  <dimension ref="A1:Y36"/>
+  <dimension ref="A1:Z36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.83203125" bestFit="1" customWidth="1"/>
@@ -2181,12 +2213,13 @@
     <col min="15" max="15" width="13.5" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="10.1640625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="0.6640625" customWidth="1"/>
-    <col min="18" max="18" width="25.5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="0.6640625" customWidth="1"/>
+    <col min="18" max="18" width="11" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="25.5" customWidth="1"/>
+    <col min="20" max="20" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="0.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="22" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>51</v>
       </c>
@@ -2220,22 +2253,23 @@
         <v>22</v>
       </c>
       <c r="S1" s="3"/>
-      <c r="T1" s="2"/>
-    </row>
-    <row r="2" spans="1:20" ht="22" x14ac:dyDescent="0.3">
+      <c r="T1" s="3"/>
+      <c r="U1" s="2"/>
+    </row>
+    <row r="2" spans="1:21" ht="22" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>52</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="14">
         <f>SUM(D6:D19)</f>
-        <v>4600</v>
+        <v>7650</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="4"/>
       <c r="F2" s="3">
         <f>SUM(G6:G19)</f>
-        <v>-340</v>
+        <v>-27</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="14">
@@ -2250,16 +2284,17 @@
       <c r="N2" s="4"/>
       <c r="O2" s="14">
         <f>SUM(P6:P20)</f>
-        <v>58589</v>
+        <v>60265</v>
       </c>
       <c r="Q2" s="4"/>
       <c r="R2" s="14">
-        <f>SUM(S6:S16)</f>
+        <f>SUM(T6:T16)</f>
         <v>38672</v>
       </c>
-      <c r="T2" s="2"/>
-    </row>
-    <row r="3" spans="1:20" ht="22" x14ac:dyDescent="0.3">
+      <c r="S2" s="14"/>
+      <c r="U2" s="2"/>
+    </row>
+    <row r="3" spans="1:21" ht="22" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>49</v>
       </c>
@@ -2287,9 +2322,10 @@
       <c r="Q3" s="4"/>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
-      <c r="T3" s="2"/>
-    </row>
-    <row r="4" spans="1:20" ht="22" x14ac:dyDescent="0.3">
+      <c r="T3" s="3"/>
+      <c r="U3" s="2"/>
+    </row>
+    <row r="4" spans="1:21" ht="22" x14ac:dyDescent="0.3">
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
         <v>25</v>
@@ -2312,9 +2348,10 @@
       <c r="Q4" s="4"/>
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
-      <c r="T4" s="2"/>
-    </row>
-    <row r="5" spans="1:20" ht="22" x14ac:dyDescent="0.3">
+      <c r="T4" s="3"/>
+      <c r="U4" s="2"/>
+    </row>
+    <row r="5" spans="1:21" ht="22" x14ac:dyDescent="0.3">
       <c r="B5" s="2"/>
       <c r="C5" s="3"/>
       <c r="D5" s="14"/>
@@ -2333,9 +2370,10 @@
       <c r="Q5" s="4"/>
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
-      <c r="T5" s="2"/>
-    </row>
-    <row r="6" spans="1:20" ht="22" x14ac:dyDescent="0.3">
+      <c r="T5" s="3"/>
+      <c r="U5" s="2"/>
+    </row>
+    <row r="6" spans="1:21" ht="22" x14ac:dyDescent="0.3">
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
         <v>26</v>
@@ -2372,15 +2410,18 @@
         <v>39948</v>
       </c>
       <c r="Q6" s="4"/>
-      <c r="R6" s="3" t="s">
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="S6" s="14">
+      <c r="T6" s="14">
         <v>187</v>
       </c>
-      <c r="T6" s="2"/>
-    </row>
-    <row r="7" spans="1:20" ht="22" x14ac:dyDescent="0.3">
+      <c r="U6" s="2"/>
+    </row>
+    <row r="7" spans="1:21" ht="22" x14ac:dyDescent="0.3">
       <c r="B7" s="2"/>
       <c r="C7" s="3">
         <v>1</v>
@@ -2415,15 +2456,18 @@
         <v>864</v>
       </c>
       <c r="Q7" s="4"/>
-      <c r="R7" s="3" t="s">
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="S7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="S7" s="14">
+      <c r="T7" s="14">
         <v>1083</v>
       </c>
-      <c r="T7" s="2"/>
-    </row>
-    <row r="8" spans="1:20" ht="22" x14ac:dyDescent="0.3">
+      <c r="U7" s="2"/>
+    </row>
+    <row r="8" spans="1:21" ht="22" x14ac:dyDescent="0.3">
       <c r="B8" s="2"/>
       <c r="C8" s="3">
         <v>1</v>
@@ -2435,7 +2479,9 @@
       <c r="F8" s="3">
         <v>2</v>
       </c>
-      <c r="G8" s="14"/>
+      <c r="G8" s="14">
+        <v>313</v>
+      </c>
       <c r="H8" s="4"/>
       <c r="I8" s="3" t="s">
         <v>31</v>
@@ -2458,20 +2504,25 @@
         <v>17777</v>
       </c>
       <c r="Q8" s="4"/>
-      <c r="R8" s="3" t="s">
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="S8" s="14">
+      <c r="T8" s="14">
         <v>721</v>
       </c>
-      <c r="T8" s="2"/>
-    </row>
-    <row r="9" spans="1:20" ht="22" x14ac:dyDescent="0.3">
+      <c r="U8" s="2"/>
+    </row>
+    <row r="9" spans="1:21" ht="22" x14ac:dyDescent="0.3">
       <c r="B9" s="2"/>
       <c r="C9" s="3">
         <v>2</v>
       </c>
-      <c r="D9" s="14"/>
+      <c r="D9" s="14">
+        <v>3050</v>
+      </c>
       <c r="E9" s="4"/>
       <c r="F9" s="3">
         <v>3</v>
@@ -2490,18 +2541,25 @@
       </c>
       <c r="M9" s="14"/>
       <c r="N9" s="4"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="14"/>
+      <c r="O9" s="3">
+        <v>2</v>
+      </c>
+      <c r="P9" s="14">
+        <v>1676</v>
+      </c>
       <c r="Q9" s="4"/>
-      <c r="R9" s="3" t="s">
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="S9" s="14">
+      <c r="T9" s="14">
         <v>4479</v>
       </c>
-      <c r="T9" s="2"/>
-    </row>
-    <row r="10" spans="1:20" ht="22" x14ac:dyDescent="0.3">
+      <c r="U9" s="2"/>
+    </row>
+    <row r="10" spans="1:21" ht="22" x14ac:dyDescent="0.3">
       <c r="B10" s="2"/>
       <c r="C10" s="3">
         <v>3</v>
@@ -2528,15 +2586,18 @@
       <c r="O10" s="3"/>
       <c r="P10" s="14"/>
       <c r="Q10" s="4"/>
-      <c r="R10" s="3" t="s">
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="S10" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="S10" s="14">
+      <c r="T10" s="14">
         <v>540</v>
       </c>
-      <c r="T10" s="2"/>
-    </row>
-    <row r="11" spans="1:20" ht="22" x14ac:dyDescent="0.3">
+      <c r="U10" s="2"/>
+    </row>
+    <row r="11" spans="1:21" ht="22" x14ac:dyDescent="0.3">
       <c r="B11" s="2"/>
       <c r="C11" s="3">
         <v>4</v>
@@ -2559,15 +2620,18 @@
       <c r="O11" s="3"/>
       <c r="P11" s="14"/>
       <c r="Q11" s="4"/>
-      <c r="R11" s="3" t="s">
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="S11" s="14">
+      <c r="T11" s="14">
         <v>3162</v>
       </c>
-      <c r="T11" s="2"/>
-    </row>
-    <row r="12" spans="1:20" ht="22" x14ac:dyDescent="0.3">
+      <c r="U11" s="2"/>
+    </row>
+    <row r="12" spans="1:21" ht="22" x14ac:dyDescent="0.3">
       <c r="B12" s="2"/>
       <c r="C12" s="3">
         <v>5</v>
@@ -2590,15 +2654,18 @@
       <c r="O12" s="3"/>
       <c r="P12" s="14"/>
       <c r="Q12" s="4"/>
-      <c r="R12" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="S12" s="14">
+      <c r="R12">
+        <v>2</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="T12" s="14">
         <v>27000</v>
       </c>
-      <c r="T12" s="2"/>
-    </row>
-    <row r="13" spans="1:20" ht="22" x14ac:dyDescent="0.3">
+      <c r="U12" s="2"/>
+    </row>
+    <row r="13" spans="1:21" ht="22" x14ac:dyDescent="0.3">
       <c r="B13" s="2"/>
       <c r="C13" s="3">
         <v>6</v>
@@ -2621,15 +2688,18 @@
       <c r="O13" s="3"/>
       <c r="P13" s="14"/>
       <c r="Q13" s="4"/>
-      <c r="R13" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="S13" s="14">
+      <c r="R13">
+        <v>2</v>
+      </c>
+      <c r="S13" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="T13" s="14">
         <v>1000</v>
       </c>
-      <c r="T13" s="2"/>
-    </row>
-    <row r="14" spans="1:20" ht="22" x14ac:dyDescent="0.3">
+      <c r="U13" s="2"/>
+    </row>
+    <row r="14" spans="1:21" ht="22" x14ac:dyDescent="0.3">
       <c r="B14" s="2"/>
       <c r="C14" s="3">
         <v>7</v>
@@ -2650,15 +2720,18 @@
       <c r="O14" s="3"/>
       <c r="P14" s="14"/>
       <c r="Q14" s="4"/>
-      <c r="R14" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="S14" s="14">
+      <c r="R14">
+        <v>2</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="T14" s="14">
         <v>500</v>
       </c>
-      <c r="T14" s="2"/>
-    </row>
-    <row r="15" spans="1:20" ht="22" x14ac:dyDescent="0.3">
+      <c r="U14" s="2"/>
+    </row>
+    <row r="15" spans="1:21" ht="22" x14ac:dyDescent="0.3">
       <c r="B15" s="2"/>
       <c r="C15" s="3">
         <v>8</v>
@@ -2680,10 +2753,11 @@
       <c r="P15" s="14"/>
       <c r="Q15" s="4"/>
       <c r="R15" s="3"/>
-      <c r="S15" s="14"/>
-      <c r="T15" s="2"/>
-    </row>
-    <row r="16" spans="1:20" ht="22" x14ac:dyDescent="0.3">
+      <c r="S15" s="3"/>
+      <c r="T15" s="14"/>
+      <c r="U15" s="2"/>
+    </row>
+    <row r="16" spans="1:21" ht="22" x14ac:dyDescent="0.3">
       <c r="B16" s="2"/>
       <c r="C16" s="3">
         <v>9</v>
@@ -2705,10 +2779,11 @@
       <c r="P16" s="14"/>
       <c r="Q16" s="4"/>
       <c r="R16" s="3"/>
-      <c r="S16" s="14"/>
-      <c r="T16" s="2"/>
-    </row>
-    <row r="17" spans="2:22" ht="22" x14ac:dyDescent="0.3">
+      <c r="S16" s="3"/>
+      <c r="T16" s="14"/>
+      <c r="U16" s="2"/>
+    </row>
+    <row r="17" spans="2:23" ht="22" x14ac:dyDescent="0.3">
       <c r="B17" s="2"/>
       <c r="C17" s="3">
         <v>10</v>
@@ -2730,10 +2805,11 @@
       <c r="P17" s="14"/>
       <c r="Q17" s="4"/>
       <c r="R17" s="3"/>
-      <c r="S17" s="14"/>
-      <c r="T17" s="2"/>
-    </row>
-    <row r="18" spans="2:22" ht="22" x14ac:dyDescent="0.3">
+      <c r="S17" s="3"/>
+      <c r="T17" s="14"/>
+      <c r="U17" s="2"/>
+    </row>
+    <row r="18" spans="2:23" ht="22" x14ac:dyDescent="0.3">
       <c r="B18" s="2"/>
       <c r="C18" s="3">
         <v>11</v>
@@ -2755,10 +2831,11 @@
       <c r="P18" s="14"/>
       <c r="Q18" s="4"/>
       <c r="R18" s="3"/>
-      <c r="S18" s="14"/>
-      <c r="T18" s="2"/>
-    </row>
-    <row r="19" spans="2:22" ht="22" x14ac:dyDescent="0.3">
+      <c r="S18" s="3"/>
+      <c r="T18" s="14"/>
+      <c r="U18" s="2"/>
+    </row>
+    <row r="19" spans="2:23" ht="22" x14ac:dyDescent="0.3">
       <c r="B19" s="2"/>
       <c r="C19" s="3">
         <v>12</v>
@@ -2778,10 +2855,11 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="4"/>
       <c r="R19" s="3"/>
-      <c r="S19" s="14"/>
-      <c r="T19" s="2"/>
-    </row>
-    <row r="20" spans="2:22" ht="22" x14ac:dyDescent="0.3">
+      <c r="S19" s="3"/>
+      <c r="T19" s="14"/>
+      <c r="U19" s="2"/>
+    </row>
+    <row r="20" spans="2:23" ht="22" x14ac:dyDescent="0.3">
       <c r="B20" s="2"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -2799,10 +2877,11 @@
       <c r="P20" s="3"/>
       <c r="Q20" s="4"/>
       <c r="R20" s="3"/>
-      <c r="S20" s="14"/>
-      <c r="T20" s="2"/>
-    </row>
-    <row r="21" spans="2:22" ht="22" x14ac:dyDescent="0.3">
+      <c r="S20" s="3"/>
+      <c r="T20" s="14"/>
+      <c r="U20" s="2"/>
+    </row>
+    <row r="21" spans="2:23" ht="22" x14ac:dyDescent="0.3">
       <c r="B21" s="2"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
@@ -2821,9 +2900,10 @@
       <c r="Q21" s="4"/>
       <c r="R21" s="4"/>
       <c r="S21" s="4"/>
-      <c r="T21" s="2"/>
-    </row>
-    <row r="22" spans="2:22" ht="22" x14ac:dyDescent="0.3">
+      <c r="T21" s="4"/>
+      <c r="U21" s="2"/>
+    </row>
+    <row r="22" spans="2:23" ht="22" x14ac:dyDescent="0.3">
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
@@ -2841,8 +2921,9 @@
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
-    </row>
-    <row r="23" spans="2:22" ht="22" x14ac:dyDescent="0.3">
+      <c r="T22" s="3"/>
+    </row>
+    <row r="23" spans="2:23" ht="22" x14ac:dyDescent="0.3">
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
@@ -2857,7 +2938,7 @@
       </c>
       <c r="M23" s="6">
         <f>O2-R2</f>
-        <v>19917</v>
+        <v>21593</v>
       </c>
       <c r="N23" s="4"/>
       <c r="O23" s="3"/>
@@ -2865,8 +2946,9 @@
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
-    </row>
-    <row r="24" spans="2:22" ht="22" x14ac:dyDescent="0.3">
+      <c r="T23" s="3"/>
+    </row>
+    <row r="24" spans="2:23" ht="22" x14ac:dyDescent="0.3">
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
@@ -2881,7 +2963,7 @@
       </c>
       <c r="M24" s="6">
         <f>C2</f>
-        <v>4600</v>
+        <v>7650</v>
       </c>
       <c r="N24" s="4"/>
       <c r="O24" s="3"/>
@@ -2889,8 +2971,9 @@
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
       <c r="S24" s="3"/>
-    </row>
-    <row r="25" spans="2:22" ht="22" x14ac:dyDescent="0.3">
+      <c r="T24" s="3"/>
+    </row>
+    <row r="25" spans="2:23" ht="22" x14ac:dyDescent="0.3">
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
@@ -2913,8 +2996,9 @@
       <c r="Q25" s="3"/>
       <c r="R25" s="3"/>
       <c r="S25" s="3"/>
-    </row>
-    <row r="26" spans="2:22" ht="22" x14ac:dyDescent="0.3">
+      <c r="T25" s="3"/>
+    </row>
+    <row r="26" spans="2:23" ht="22" x14ac:dyDescent="0.3">
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
@@ -2937,11 +3021,12 @@
       <c r="Q26" s="3"/>
       <c r="R26" s="3"/>
       <c r="S26" s="3"/>
-      <c r="V26" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="27" spans="2:22" ht="22" x14ac:dyDescent="0.3">
+      <c r="T26" s="3"/>
+      <c r="W26" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="27" spans="2:23" ht="22" x14ac:dyDescent="0.3">
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -2963,15 +3048,16 @@
       <c r="Q27" s="3"/>
       <c r="R27" s="3"/>
       <c r="S27" s="3"/>
-      <c r="U27">
+      <c r="T27" s="3"/>
+      <c r="V27">
         <v>35266</v>
       </c>
-      <c r="V27" s="15">
-        <f>M29-U27</f>
-        <v>-21441</v>
-      </c>
-    </row>
-    <row r="28" spans="2:22" ht="22" x14ac:dyDescent="0.3">
+      <c r="W27" s="15">
+        <f>M29-V27</f>
+        <v>-16402</v>
+      </c>
+    </row>
+    <row r="28" spans="2:23" ht="22" x14ac:dyDescent="0.3">
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
@@ -2986,7 +3072,7 @@
       </c>
       <c r="M28" s="6">
         <f>F2</f>
-        <v>-340</v>
+        <v>-27</v>
       </c>
       <c r="N28" s="4"/>
       <c r="O28" s="3"/>
@@ -2994,8 +3080,9 @@
       <c r="Q28" s="3"/>
       <c r="R28" s="3"/>
       <c r="S28" s="3"/>
-    </row>
-    <row r="29" spans="2:22" ht="22" x14ac:dyDescent="0.3">
+      <c r="T28" s="3"/>
+    </row>
+    <row r="29" spans="2:23" ht="22" x14ac:dyDescent="0.3">
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
@@ -3010,7 +3097,7 @@
       </c>
       <c r="M29" s="6">
         <f>SUM(M23:M28)</f>
-        <v>13825</v>
+        <v>18864</v>
       </c>
       <c r="N29" s="4"/>
       <c r="O29" s="3"/>
@@ -3018,8 +3105,9 @@
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
-    </row>
-    <row r="30" spans="2:22" ht="22" x14ac:dyDescent="0.3">
+      <c r="T29" s="3"/>
+    </row>
+    <row r="30" spans="2:23" ht="22" x14ac:dyDescent="0.3">
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
@@ -3033,8 +3121,9 @@
       <c r="Q30" s="3"/>
       <c r="R30" s="3"/>
       <c r="S30" s="3"/>
-    </row>
-    <row r="31" spans="2:22" ht="22" x14ac:dyDescent="0.3">
+      <c r="T30" s="3"/>
+    </row>
+    <row r="31" spans="2:23" ht="22" x14ac:dyDescent="0.3">
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
@@ -3048,9 +3137,10 @@
       <c r="Q31" s="3"/>
       <c r="R31" s="5"/>
       <c r="S31" s="5"/>
-    </row>
-    <row r="36" spans="25:25" x14ac:dyDescent="0.2">
-      <c r="Y36">
+      <c r="T31" s="5"/>
+    </row>
+    <row r="36" spans="26:26" x14ac:dyDescent="0.2">
+      <c r="Z36">
         <f>SUM('مصاريف الشهر'!E7:E15)</f>
         <v>1260</v>
       </c>

--- a/February 2026.xlsx
+++ b/February 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abutalib/Projects/personal-accounting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35CAA92E-D3D3-0046-A520-6463395E2F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16BBE96B-23BB-744B-8AEF-CEEB402A3EF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19800" activeTab="1" xr2:uid="{7E62CB60-3E82-0E48-87C0-051D0E492E72}"/>
   </bookViews>
@@ -582,13 +582,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -990,14 +990,14 @@
       <c r="D1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18" t="s">
+      <c r="F1" s="19"/>
+      <c r="G1" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="H1" s="18"/>
+      <c r="H1" s="19"/>
       <c r="I1" s="4"/>
       <c r="J1" s="3" t="s">
         <v>17</v>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="W2" s="3">
         <f>SUM(W7:W16)</f>
-        <v>17607</v>
+        <v>34607</v>
       </c>
       <c r="X2" s="4"/>
       <c r="Y2" s="3" t="s">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AA2" s="3">
         <f>SUM(AA7:AB41)</f>
-        <v>32533</v>
+        <v>49533</v>
       </c>
       <c r="AB2" s="4"/>
       <c r="AC2" s="3" t="s">
@@ -1190,10 +1190,10 @@
       <c r="O6" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="17" t="s">
+      <c r="P6" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="Q6" s="17"/>
+      <c r="Q6" s="18"/>
       <c r="R6" s="9"/>
       <c r="U6" s="9"/>
       <c r="X6" s="9"/>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="W12" s="3">
         <f>J32</f>
-        <v>12568</v>
+        <v>29568</v>
       </c>
       <c r="X12" s="4"/>
       <c r="AB12" s="4"/>
@@ -1727,7 +1727,7 @@
         <v>150</v>
       </c>
       <c r="I18" s="4"/>
-      <c r="J18" s="19" t="s">
+      <c r="J18" s="17" t="s">
         <v>11</v>
       </c>
       <c r="K18" s="3">
@@ -1808,7 +1808,7 @@
         <v>70</v>
       </c>
       <c r="I21" s="4"/>
-      <c r="J21" s="19" t="s">
+      <c r="J21" s="17" t="s">
         <v>14</v>
       </c>
       <c r="K21" s="3">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="AA31" s="10">
         <f>W2</f>
-        <v>17607</v>
+        <v>34607</v>
       </c>
       <c r="AB31" s="3"/>
     </row>
@@ -2049,7 +2049,7 @@
       <c r="I32" s="3"/>
       <c r="J32" s="3">
         <f>الأرصدة!M29-'مصاريف الشهر'!D32</f>
-        <v>12568</v>
+        <v>29568</v>
       </c>
       <c r="O32" s="3">
         <f>E3</f>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="Q32" s="3">
         <f>J32-SUM(O32:P32)</f>
-        <v>5039</v>
+        <v>22039</v>
       </c>
       <c r="R32" s="3"/>
       <c r="U32" s="3"/>
@@ -2148,7 +2148,7 @@
       </c>
     </row>
     <row r="43" spans="3:28" x14ac:dyDescent="0.3">
-      <c r="Y43" s="19" t="s">
+      <c r="Y43" s="17" t="s">
         <v>14</v>
       </c>
       <c r="Z43" s="3">
@@ -2156,7 +2156,7 @@
       </c>
     </row>
     <row r="44" spans="3:28" x14ac:dyDescent="0.3">
-      <c r="Y44" s="19" t="s">
+      <c r="Y44" s="17" t="s">
         <v>11</v>
       </c>
       <c r="Z44" s="3">
@@ -2289,7 +2289,7 @@
       <c r="Q2" s="4"/>
       <c r="R2" s="14">
         <f>SUM(T6:T16)</f>
-        <v>38672</v>
+        <v>21672</v>
       </c>
       <c r="S2" s="14"/>
       <c r="U2" s="2"/>
@@ -2661,7 +2661,7 @@
         <v>119</v>
       </c>
       <c r="T12" s="14">
-        <v>27000</v>
+        <v>10000</v>
       </c>
       <c r="U12" s="2"/>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="M23" s="6">
         <f>O2-R2</f>
-        <v>21593</v>
+        <v>38593</v>
       </c>
       <c r="N23" s="4"/>
       <c r="O23" s="3"/>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="W27" s="15">
         <f>M29-V27</f>
-        <v>-16402</v>
+        <v>598</v>
       </c>
     </row>
     <row r="28" spans="2:23" ht="22" x14ac:dyDescent="0.3">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="M29" s="6">
         <f>SUM(M23:M28)</f>
-        <v>18864</v>
+        <v>35864</v>
       </c>
       <c r="N29" s="4"/>
       <c r="O29" s="3"/>
